--- a/deliverables/BCFA_Manual_Test_Workbook.xlsx
+++ b/deliverables/BCFA_Manual_Test_Workbook.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defects" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$P$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$P$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -677,27 +677,27 @@
         </is>
       </c>
       <c r="B2" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A2)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A2)</f>
         <v/>
       </c>
       <c r="C2" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A2,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A2,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D2" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A2,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A2,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E2" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A2,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A2,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F2" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A2,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A2,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G2" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A2,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A2,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -708,27 +708,27 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A3)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A3)</f>
         <v/>
       </c>
       <c r="C3" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A3,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A3,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D3" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A3,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A3,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E3" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A3,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A3,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F3" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A3,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A3,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G3" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A3,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A3,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -739,27 +739,27 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A4)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A4)</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A4,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A4,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D4" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A4,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A4,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A4,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A4,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F4" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A4,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A4,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G4" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A4,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A4,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -770,27 +770,27 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A5)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A5,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A5,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A5,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A5,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A5,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A5,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A5,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A5,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G5" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A5,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A5,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -801,27 +801,27 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A6)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A6,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A6,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A6,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A6,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A6,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A6,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A6,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A6,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G6" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A6,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A6,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -832,27 +832,27 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A7)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A7,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A7,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A7,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A7,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A7,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A7,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A7,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A7,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G7" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A7,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A7,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -863,27 +863,27 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A8)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A8,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A8,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A8,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A8,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A8,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A8,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A8,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A8,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G8" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A8,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A8,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -894,27 +894,27 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A9)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A9,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A9,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A9,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A9,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A9,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A9,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F9" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A9,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A9,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G9" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A9,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A9,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -925,27 +925,27 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A10)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A10,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A10,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A10,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A10,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A10,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A10,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A10,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A10,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G10" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A10,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A10,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -956,27 +956,27 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A11)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A11,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A11,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A11,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A11,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E11" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A11,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A11,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F11" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A11,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A11,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G11" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A11,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A11,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -987,27 +987,27 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A12)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A12)</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A12,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A12,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A12,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A12,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A12,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A12,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A12,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A12,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G12" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A12,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A12,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1018,27 +1018,27 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A13)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A13)</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A13,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A13,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A13,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A13,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A13,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A13,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A13,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A13,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G13" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A13,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A13,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1049,27 +1049,27 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A14)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A14)</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A14,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A14,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A14,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A14,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A14,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A14,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A14,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A14,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G14" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A14,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A14,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1080,27 +1080,27 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A15)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A15)</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A15,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A15,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A15,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A15,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A15,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A15,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A15,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A15,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G15" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A15,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A15,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1111,27 +1111,27 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A16)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A16)</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A16,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A16,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A16,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A16,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A16,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A16,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A16,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A16,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G16" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A16,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A16,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1142,27 +1142,27 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A17)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A17)</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A17,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A17,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A17,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A17,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A17,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A17,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A17,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A17,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G17" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A17,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A17,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1173,27 +1173,27 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A18)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A18)</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A18,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A18,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A18,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A18,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A18,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A18,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A18,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A18,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G18" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A18,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A18,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1204,27 +1204,27 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A19)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A19)</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A19,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A19,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A19,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A19,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A19,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A19,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A19,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A19,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G19" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A19,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A19,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1235,27 +1235,27 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A20)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A20)</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A20,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A20,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A20,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A20,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A20,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A20,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A20,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A20,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G20" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A20,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A20,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1266,27 +1266,27 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A21)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A21)</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A21,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A21,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A21,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A21,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A21,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A21,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A21,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A21,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G21" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A21,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A21,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1297,27 +1297,27 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A22)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A22)</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A22,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A22,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A22,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A22,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A22,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A22,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A22,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A22,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G22" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A22,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A22,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1328,27 +1328,27 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A23)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A23)</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A23,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A23,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A23,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A23,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A23,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A23,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A23,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A23,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G23" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A23,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A23,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1359,27 +1359,27 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A24)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A24)</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A24,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A24,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A24,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A24,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A24,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A24,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A24,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A24,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G24" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A24,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A24,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1390,27 +1390,27 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A25)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A25)</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A25,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A25,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A25,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A25,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A25,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A25,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A25,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A25,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G25" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A25,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A25,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1421,27 +1421,27 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A26)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A26)</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A26,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A26,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A26,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A26,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A26,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A26,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A26,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A26,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G26" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A26,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A26,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1452,27 +1452,27 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A27)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A27)</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A27,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A27,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A27,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A27,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A27,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A27,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A27,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A27,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G27" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A27,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A27,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1483,27 +1483,27 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A28)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A28)</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A28,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A28,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A28,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A28,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A28,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A28,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A28,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A28,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G28" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A28,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A28,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1514,27 +1514,27 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A29)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A29)</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A29,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A29,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A29,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A29,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A29,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A29,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A29,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A29,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G29" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A29,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A29,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1545,27 +1545,27 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A30)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A30)</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A30,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A30,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A30,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A30,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A30,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A30,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A30,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A30,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G30" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A30,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A30,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1576,27 +1576,27 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A31)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A31)</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A31,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A31,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A31,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A31,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A31,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A31,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A31,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A31,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G31" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A31,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A31,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1607,27 +1607,27 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A32)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A32)</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A32,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A32,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A32,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A32,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A32,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A32,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A32,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A32,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G32" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A32,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A32,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1638,27 +1638,27 @@
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF('Test Cases'!B2:B94,A33)</f>
+        <f>COUNTIF('Test Cases'!B2:B95,A33)</f>
         <v/>
       </c>
       <c r="C33" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A33,'Test Cases'!L2:L94,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A33,'Test Cases'!L2:L95,"Pass")</f>
         <v/>
       </c>
       <c r="D33" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A33,'Test Cases'!L2:L94,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A33,'Test Cases'!L2:L95,"Fail")</f>
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A33,'Test Cases'!L2:L94,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A33,'Test Cases'!L2:L95,"Blocked")</f>
         <v/>
       </c>
       <c r="F33" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A33,'Test Cases'!L2:L94,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A33,'Test Cases'!L2:L95,"Not Run")</f>
         <v/>
       </c>
       <c r="G33" s="5">
-        <f>COUNTIFS('Test Cases'!B2:B94,A33,'Test Cases'!L2:L94,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!B2:B95,A33,'Test Cases'!L2:L95,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P94"/>
+  <dimension ref="A1:P95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Extraction JSON shows Elbtal Fachverlag GmbH, R-2026-3391, EUR, net 2058.80, tax 144.12, total 2202.92, rate 7, 2 lines. Intake goes to Review Required: vendor could not be resolved (the vendor is not in the demo master data) — expected.</t>
+          <t>Extraction JSON shows Elbtal Fachverlag GmbH, R-2026-3391, EUR, net 2058.80, tax 144.12, total 2202.92, rate 7, 2 lines. Intake Completed and an AP invoice is created with Vendor (Printed) Elbtal Fachverlag GmbH; the invoice goes to EXCEPTION Vendor Invalid (the vendor is not in the demo master data) — expected.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Extraction JSON</t>
+          <t>Extraction JSON, invoice and exception</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr"/>
@@ -7358,17 +7358,17 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>P41-CS-01</t>
+          <t>P41-INV</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Client samples</t>
+          <t>AP · Intake</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Latin-script invoices</t>
+          <t>Unknown vendor / PO: invoice created, exception on the invoice</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -7388,22 +7388,24 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Client pack (ask the BCFA team; not in source control).</t>
+          <t>Fixture test/fixtures/AP_INV_107_TH_VAT7.pdf (Thai, vendor and PO not in master data).</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>1. Upload CS-02, CS-12, CS-16, CS-22 as AP Invoice; Process Document; wait 1-2 minutes.</t>
+          <t>1. New intake, AP Invoice, attach, Process Document; wait 1-2 minutes; refresh.
+2. Open the AP invoice.
+3. (Admin) create the vendor with exactly the printed name; Re-run Validation.</t>
         </is>
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>Critical fields as in CLIENT_DOCUMENT_TEST_MATRIX.md; review only because the vendor is not in the POC master data.</t>
+          <t>Intake Completed; invoice created with Vendor (Printed), PO Number (Printed), 3 lines; EXCEPTION Vendor Invalid naming the printed vendor. After step 3: vendor linked; new exception PO Mismatch (printed PO not found) until the PO exists.</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>Intakes</t>
+          <t>Invoice, exceptions</t>
         </is>
       </c>
       <c r="K90" s="8" t="inlineStr"/>
@@ -7420,7 +7422,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>P41-CS-02</t>
+          <t>P41-CS-01</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -7430,7 +7432,7 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Payment advices with per-invoice lines</t>
+          <t>Latin-script invoices</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -7445,22 +7447,22 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>AR Processor (bcfa.ar.processor)</t>
+          <t>AP Processor (bcfa.ap.processor)</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>Client pack.</t>
+          <t>Client pack (ask the BCFA team; not in source control).</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>1. Upload CS-04, CS-05, CS-09 as AR Payment Advice; Process Document.</t>
+          <t>1. Upload CS-02, CS-12, CS-16, CS-22 as AP Invoice; Process Document; wait 1-2 minutes.</t>
         </is>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>Payer, reference, amount, currency read; per-invoice lines reconcile to the payment (CS-04: TDS per invoice); review only for the customer master data.</t>
+          <t>Critical fields as in CLIENT_DOCUMENT_TEST_MATRIX.md; review only because the vendor is not in the POC master data.</t>
         </is>
       </c>
       <c r="J91" s="9" t="inlineStr">
@@ -7482,7 +7484,7 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>P41-CS-03</t>
+          <t>P41-CS-02</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
@@ -7492,42 +7494,42 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Large package</t>
+          <t>Payment advices with per-invoice lines</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>AP Processor (bcfa.ap.processor)</t>
+          <t>AR Processor (bcfa.ar.processor)</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Client pack, CS-28 (14.7 MB).</t>
+          <t>Client pack.</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>1. Upload as AP Invoice; Process Document.</t>
+          <t>1. Upload CS-04, CS-05, CS-09 as AR Payment Advice; Process Document.</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>Review: "native extraction accepts up to 4 MB per file. Upload the invoice pages only"; nothing extracted.</t>
+          <t>Payer, reference, amount, currency read; per-invoice lines reconcile to the payment (CS-04: TDS per invoice); review only for the customer master data.</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>Intake message</t>
+          <t>Intakes</t>
         </is>
       </c>
       <c r="K92" s="8" t="inlineStr"/>
@@ -7544,7 +7546,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>P41-CS-04</t>
+          <t>P41-CS-03</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -7554,7 +7556,7 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Not an invoice</t>
+          <t>Large package</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -7574,7 +7576,7 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>Client pack, CS-23 (PO + GRN only).</t>
+          <t>Client pack, CS-28 (14.7 MB).</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
@@ -7584,12 +7586,12 @@
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>Review; no invoice number, vendor or amount invented.</t>
+          <t>Review: "native extraction accepts up to 4 MB per file. Upload the invoice pages only"; nothing extracted.</t>
         </is>
       </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>Intake</t>
+          <t>Intake message</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr"/>
@@ -7606,7 +7608,7 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>P41-CS-05</t>
+          <t>P41-CS-04</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
@@ -7616,12 +7618,12 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Chinese / Korean / Thai invoices (known platform limitation)</t>
+          <t>Not an invoice</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -7636,7 +7638,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>Client pack, CS-18, CS-19, CS-26.</t>
+          <t>Client pack, CS-23 (PO + GRN only).</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -7646,12 +7648,12 @@
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>Fields not read are left empty (no value invented); confidence low; review. See MULTILINGUAL_DOCUMENT_INTELLIGENCE_READINESS.md.</t>
+          <t>Review; no invoice number, vendor or amount invented.</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>Intakes</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="K94" s="8" t="inlineStr"/>
@@ -7665,9 +7667,71 @@
       <c r="O94" s="8" t="inlineStr"/>
       <c r="P94" s="8" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>P41-CS-05</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>Client samples</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>Chinese / Korean / Thai invoices (known platform limitation)</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>AP Processor (bcfa.ap.processor)</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>Client pack, CS-18, CS-19, CS-26.</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>1. Upload as AP Invoice; Process Document.</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>Fields not read are left empty (no value invented); confidence low; review. See MULTILINGUAL_DOCUMENT_INTELLIGENCE_READINESS.md.</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>Intakes</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="inlineStr"/>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M95" s="9" t="inlineStr"/>
+      <c r="N95" s="9" t="inlineStr"/>
+      <c r="O95" s="9" t="inlineStr"/>
+      <c r="P95" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P94"/>
-  <conditionalFormatting sqref="L2:L94">
+  <autoFilter ref="A1:P95"/>
+  <conditionalFormatting sqref="L2:L95">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -7679,7 +7743,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="L2:L95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/deliverables/BCFA_Manual_Test_Workbook.xlsx
+++ b/deliverables/BCFA_Manual_Test_Workbook.xlsx
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Explain with Now Assist (advisory)</t>
+          <t>Explain with AI (advisory)</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>1. On an open AP exception click Explain with Now Assist; wait up to 60 s; refresh.</t>
+          <t>1. On an open AP exception click Explain with AI; wait up to 60 s; refresh.</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
